--- a/Assessment Questions/CDS/BIA - 119/Connecting to Various Data Sources_/Connecting to a Webpage/_Connecting to a Webpage.xlsx
+++ b/Assessment Questions/CDS/BIA - 119/Connecting to Various Data Sources_/Connecting to a Webpage/_Connecting to a Webpage.xlsx
@@ -1,135 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>Dataset_Name,URL,Description,Data_Type,Expected_Columns,Update_Frequency</t>
-  </si>
-  <si>
-    <t>Sales_Data_API,https://raw.githubusercontent.com/datasets/sales-data/main/sales.json,"JSON API endpoint containing sales transactions",JSON,10,Daily</t>
-  </si>
-  <si>
-    <t>Product_Catalog,https://example.com/api/products.xml,"XML product catalog feed",XML,8,Weekly</t>
-  </si>
-  <si>
-    <t>Stock_Prices,https://api.stockdata.org/v1/data/quote?symbols=AAPL,GOOGL,MSFT,"Live stock price API",JSON,12,Real-time</t>
-  </si>
-  <si>
-    <t>Weather_Data,https://api.weather.gov/points/40.7128,-74.0060,"Weather forecast data",JSON,15,Hourly</t>
-  </si>
-  <si>
-    <t>News_Feed,https://rss.nytimes.com/services/xml/rss/nyt/HomePage.xml,"RSS news feed",XML,6,Hourly</t>
-  </si>
-  <si>
-    <t>Customer_Reviews,https://api.reviews.com/v1/products/12345/reviews,"Customer reviews API",JSON,8,Daily</t>
-  </si>
-  <si>
-    <t>Currency_Rates,https://api.exchangerate-api.com/v4/latest/USD,"Currency exchange rates",JSON,5,Hourly</t>
-  </si>
-  <si>
-    <t>Population_Data,https://data.census.gov/api/data/2023/acs/acs5?get=NAME,B01001_001E&amp;for=state:*,"Census data API",JSON,4,Yearly</t>
-  </si>
-  <si>
-    <t>GitHub_Commits,https://api.github.com/repos/microsoft/PowerBI-Developer-Samples/commits,"GitHub API commits",JSON,12,Real-time</t>
-  </si>
-  <si>
-    <t>Wikipedia_Tables,https://en.wikipedia.org/wiki/List_of_countries_by_GDP_(nominal),"Wikipedia data tables",HTML Table,7,Quarterly</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Web_Connection_Type,Steps_to_Perform,Expected_Result,Key_Considerations</t>
-  </si>
-  <si>
-    <t>1,"Connect to the sample JSON API: https://jsonplaceholder.typicode.com/posts. Load the data into Power BI. How many posts are returned?","JSON API","Get Data → Web → Enter URL → Select 'posts' table → Load","100 posts loaded with fields: userId, id, title, body","JSON data may have nested structures; Use 'List' or 'Record' expansion"</t>
-  </si>
-  <si>
-    <t>2,"Connect to the same JSON API but use Transform Data instead of Load. Explore the nested structure. Expand the records to create a flat table.","JSON with Expansion","Get Data → Web → Enter URL → Transform → Click on 'List' → To Table → Expand Record","Flat table with all fields expanded","Use 'Expand' button on Record columns; Handle multiple levels of nesting"</t>
-  </si>
-  <si>
-    <t>3,"Connect to an XML feed: https://www.w3schools.com/xml/note.xml. Load the XML data. How many elements are in the XML structure?","XML Feed","Get Data → Web → Enter URL → Select 'note' table → Load","XML data with elements: to, from, heading, body","XML structure shown in Navigator; Select appropriate table level"</t>
-  </si>
-  <si>
-    <t>4,"Connect to a webpage with HTML tables: https://en.wikipedia.org/wiki/List_of_S%26P_500_companies. Extract the main table of S&amp;P 500 companies. How many companies are listed?","HTML Table","Get Data → Web → Enter URL → Select Table 0 → Load","505 companies loaded with ticker, company name, sector, etc.","Preview shows all tables on page; Select correct table number"</t>
-  </si>
-  <si>
-    <t>5,"Connect to a webpage with multiple tables: https://www.boxofficemojo.com/year/2024/. Extract the 'Top 2024 Movies' table.","Multiple HTML Tables","Get Data → Web → Enter URL → Select correct table (Table 2) → Load","Top movies table with rank, title, gross, etc.","Use Navigator to preview each table; Table numbers may change"</t>
-  </si>
-  <si>
-    <t>6,"Connect to a REST API that requires an API key: https://api.example.com/data?apikey=YOUR_KEY. Add the API key as a parameter in the URL.","API with Authentication","Get Data → Web → Enter URL with apikey parameter → Load","Data loads successfully with API key","Store API keys securely; Use parameters for keys; Consider Power BI dataflows"</t>
-  </si>
-  <si>
-    <t>7,"Connect to a GitHub API endpoint: https://api.github.com/repos/microsoft/PowerBI-visuals/commits. Load the commits data. How many commits are in the response?","GitHub API","Get Data → Web → Enter URL → Transform → Expand records","20 commits per page (default) with commit details","GitHub API has pagination; Use headers to get more records"</t>
-  </si>
-  <si>
-    <t>8,"Connect to a JSON API that returns nested data: https://datausa.io/api/data?drilldowns=State&amp;measures=Population. Expand the nested 'data' array to get population figures.","Nested JSON","Get Data → Web → Enter URL → Select 'data' list → To Table → Expand","Population data for all US states","API returns metadata and data; Focus on the data array"</t>
-  </si>
-  <si>
-    <t>9,"Connect to an RSS feed: https://feeds.feedburner.com/TechCrunch. Extract the latest 10 news items.","RSS Feed","Get Data → Web → Enter URL → Select 'channel' → Expand 'item' list","10 latest TechCrunch articles with title, link, description","RSS feeds are XML; Navigate to 'item' elements"</t>
-  </si>
-  <si>
-    <t>10,"Connect to a webpage and use 'Web.View' to see available tables. Select a specific table by its CSS selector if available.","CSS Selector","Get Data → Web → Enter URL → Advanced → Select by CSS → Enter selector","Table filtered by CSS selector","Use browser DevTools to find CSS selector; Advanced option available"</t>
-  </si>
-  <si>
-    <t>11,"Connect to a JSON API that returns paginated results. Modify the URL to get page 2 of results: https://jsonplaceholder.typicode.com/posts?_page=2","Pagination","Get Data → Web → Enter URL with _page=2 → Load","Posts 11-20 loaded","Many APIs use pagination; Create function to loop through pages"</t>
-  </si>
-  <si>
-    <t>12,"Connect to a webpage that requires authentication. Use Windows Authentication for an internal SharePoint page.","Windows Authentication","Get Data → Web → Enter URL → Windows Authentication → Sign in","Page loads with current Windows credentials","Requires appropriate permissions; Works with internal sites"</t>
-  </si>
-  <si>
-    <t>13,"Connect to a webpage that uses OAuth 2.0 authentication (e.g., Microsoft Graph API). Configure the OAuth settings.","OAuth 2.0","Get Data → Web → Enter URL → OAuth 2.0 → Sign in → Grant permissions","Data loads after authentication","Requires registered application; Redirect URI configuration"</t>
-  </si>
-  <si>
-    <t>14,"Connect to a webpage and load data from an iframe or embedded content. Navigate to the actual data source URL.","Iframe Content","Inspect page → Find iframe src → Connect to that URL directly","Data loads from embedded source","Use browser DevTools to find actual data URL; Iframe content is separate"</t>
-  </si>
-  <si>
-    <t>15,"Connect to a webpage and use the 'Table Statistics' view to see row counts and preview data before loading.","Table Statistics","Get Data → Web → Enter URL → Select table → Table Statistics view","Row count and column statistics displayed","Helps understand data size; Plan transformations"</t>
-  </si>
-  <si>
-    <t>16,"Connect to a webpage that returns data in CSV format directly (e.g., https://sample-videos.com/csv/Sample-Spreadsheet-10-rows.csv). Load the CSV from web.","Web CSV","Get Data → Web → Enter CSV URL → Load","CSV data loaded as table","Same as CSV import; Web connector handles CSV files"</t>
-  </si>
-  <si>
-    <t>17,"Connect to a webpage and create a function to scrape data from multiple pages. Create a custom function that takes page number as parameter.","Custom Web Function","Create blank query → Write function: (page) =&gt; Web.Page(Web.Contents(URL &amp; page))","Function returns data for any page","Use for paginated websites; Combine pages with List.Combine"</t>
-  </si>
-  <si>
-    <t>18,"Connect to a webpage that requires a user agent header. Add custom headers in the Web.Contents M function.","Custom Headers","Advanced Editor → Web.Contents(URL, [Headers=[UserAgent='Power BI']])","Request sent with custom headers","Some sites require specific User-Agent; Add authentication headers"</t>
-  </si>
-  <si>
-    <t>19,"Connect to a JSON API and extract data from a specific nested path. Use the 'Parse JSON' function and navigate to the desired record.","JSON Path Navigation","Get Data → Web → Transform → Parse JSON → Drill down to specific path","Data extracted from nested structure","Use 'Record.Field' or drill down in Query Editor"</t>
-  </si>
-  <si>
-    <t>20,"Connect to a webpage and schedule refresh for the dataset. Configure the data source credentials for automatic refresh in Power BI Service.","Scheduled Refresh","Publish to Service → Dataset Settings → Data Source Credentials → Schedule Refresh","Dataset refreshes automatically","Credentials must be saved; Gateway required for on-premises"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -139,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -363,185 +316,693 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset_Name,URL,Description,Data_Type,Expected_Columns,Update_Frequency</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Sales_Data_API,https://raw.githubusercontent.com/datasets/sales-data/main/sales.json,"JSON API endpoint containing sales transactions",JSON,10,Daily</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Product_Catalog,https://example.com/api/products.xml,"XML product catalog feed",XML,8,Weekly</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Stock_Prices,https://api.stockdata.org/v1/data/quote?symbols=AAPL,GOOGL,MSFT,"Live stock price API",JSON,12,Real-time</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Weather_Data,https://api.weather.gov/points/40.7128,-74.0060,"Weather forecast data",JSON,15,Hourly</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>News_Feed,https://rss.nytimes.com/services/xml/rss/nyt/HomePage.xml,"RSS news feed",XML,6,Hourly</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Customer_Reviews,https://api.reviews.com/v1/products/12345/reviews,"Customer reviews API",JSON,8,Daily</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Currency_Rates,https://api.exchangerate-api.com/v4/latest/USD,"Currency exchange rates",JSON,5,Hourly</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Population_Data,https://data.census.gov/api/data/2023/acs/acs5?get=NAME,B01001_001E&amp;for=state:*,"Census data API",JSON,4,Yearly</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GitHub_Commits,https://api.github.com/repos/microsoft/PowerBI-Developer-Samples/commits,"GitHub API commits",JSON,12,Real-time</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Wikipedia_Tables,https://en.wikipedia.org/wiki/List_of_countries_by_GDP_(nominal),"Wikipedia data tables",HTML Table,7,Quarterly</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the sample JSON API: https://jsonplaceholder.typicode.com/posts. Load the data into Power BI. How many posts are returned?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Connect to the same JSON API but use Transform Data instead of Load. Explore the nested structure. Expand the records to create a flat table.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Connect to an XML feed: https://www.w3schools.com/xml/note.xml. Load the XML data. How many elements are in the XML structure?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage with HTML tables: https://en.wikipedia.org/wiki/List_of_S%26P_500_companies. Extract the main table of S&amp;P 500 companies. How many companies are listed?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage with multiple tables: https://www.boxofficemojo.com/year/2024/. Extract the 'Top 2024 Movies' table.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a REST API that requires an API key: https://api.example.com/data?apikey=YOUR_KEY. Add the API key as a parameter in the URL.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a GitHub API endpoint: https://api.github.com/repos/microsoft/PowerBI-visuals/commits. Load the commits data. How many commits are in the response?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a JSON API that returns nested data: https://datausa.io/api/data?drilldowns=State&amp;measures=Population. Expand the nested 'data' array to get population figures.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Connect to an RSS feed: https://feeds.feedburner.com/TechCrunch. Extract the latest 10 news items.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage and use 'Web.View' to see available tables. Select a specific table by its CSS selector if available.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a JSON API that returns paginated results. Modify the URL to get page 2 of results: https://jsonplaceholder.typicode.com/posts?_page=2</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage that requires authentication. Use Windows Authentication for an internal SharePoint page.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage that uses OAuth 2.0 authentication (e.g., Microsoft Graph API). Configure the OAuth settings.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage and load data from an iframe or embedded content. Navigate to the actual data source URL.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage and use the 'Table Statistics' view to see row counts and preview data before loading.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage that returns data in CSV format directly (e.g., https://sample-videos.com/csv/Sample-Spreadsheet-10-rows.csv). Load the CSV from web.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage and create a function to scrape data from multiple pages. Create a custom function that takes page number as parameter.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage that requires a user agent header. Add custom headers in the Web.Contents M function.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a JSON API and extract data from a specific nested path. Use the 'Parse JSON' function and navigate to the desired record.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>_Connecting to a Webpage</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Connect to a webpage and schedule refresh for the dataset. Configure the data source credentials for automatic refresh in Power BI Service.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>